--- a/Bike-Repair-Source-Workbooks/Cash-Flow-Steps.xlsx
+++ b/Bike-Repair-Source-Workbooks/Cash-Flow-Steps.xlsx
@@ -5,12 +5,12 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/ra1/Courses-Local/Instructional_Redesign_v2/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/ra1/Courses-Local/Instructional_Redesign_v2/Bike-Repair-Source-Workbooks/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{23DCD215-2F3C-9245-BD55-B6986F27E67F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="11_6A0B6C525C32D5C9722AA8CA2AB4C9B86DCEA4DE" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="11680" yWindow="3800" windowWidth="24600" windowHeight="20940" activeTab="3" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="11680" yWindow="3800" windowWidth="24600" windowHeight="20940" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="0 · Data copied in" sheetId="1" r:id="rId1"/>
@@ -44,6 +44,51 @@
     <t>For the period June 1 – August 31, 2026</t>
   </si>
   <si>
+    <t>Operating activities</t>
+  </si>
+  <si>
+    <t>Collected from repair customers</t>
+  </si>
+  <si>
+    <t>Parts purchased</t>
+  </si>
+  <si>
+    <t>Rent paid</t>
+  </si>
+  <si>
+    <t>Cash from operating activities</t>
+  </si>
+  <si>
+    <t>Investing activities</t>
+  </si>
+  <si>
+    <t>Purchased repair tool</t>
+  </si>
+  <si>
+    <t>Cash used in investing activities</t>
+  </si>
+  <si>
+    <t>Financing activities</t>
+  </si>
+  <si>
+    <t>Paid off credit card</t>
+  </si>
+  <si>
+    <t>Owner's draw</t>
+  </si>
+  <si>
+    <t>Cash used in financing activities</t>
+  </si>
+  <si>
+    <t>Net change in cash</t>
+  </si>
+  <si>
+    <t>Cash, June 1, 2026</t>
+  </si>
+  <si>
+    <t>Cash, August 31, 2026</t>
+  </si>
+  <si>
     <t>Repair collected — Dana R.</t>
   </si>
   <si>
@@ -153,51 +198,6 @@
   </si>
   <si>
     <t>Financing</t>
-  </si>
-  <si>
-    <t>Operating activities</t>
-  </si>
-  <si>
-    <t>Cash from operating activities</t>
-  </si>
-  <si>
-    <t>Investing activities</t>
-  </si>
-  <si>
-    <t>Cash used in investing activities</t>
-  </si>
-  <si>
-    <t>Financing activities</t>
-  </si>
-  <si>
-    <t>Cash used in financing activities</t>
-  </si>
-  <si>
-    <t>Net change in cash</t>
-  </si>
-  <si>
-    <t>Collected from repair customers</t>
-  </si>
-  <si>
-    <t>Parts purchased</t>
-  </si>
-  <si>
-    <t>Rent paid</t>
-  </si>
-  <si>
-    <t>Purchased repair tool</t>
-  </si>
-  <si>
-    <t>Paid off credit card</t>
-  </si>
-  <si>
-    <t>Owner's draw</t>
-  </si>
-  <si>
-    <t>Cash, June 1, 2026</t>
-  </si>
-  <si>
-    <t>Cash, August 31, 2026</t>
   </si>
 </sst>
 </file>
@@ -207,7 +207,7 @@
   <numFmts count="3">
     <numFmt numFmtId="41" formatCode="_(* #,##0_);_(* \(#,##0\);_(* &quot;-&quot;_);_(@_)"/>
     <numFmt numFmtId="164" formatCode="\$#,##0;\(\$#,##0\)"/>
-    <numFmt numFmtId="168" formatCode="_(&quot;$&quot;* #,##0_);_(&quot;$&quot;* \(#,##0\);_(&quot;$&quot;* &quot;-&quot;??_);_(@_)"/>
+    <numFmt numFmtId="165" formatCode="_(&quot;$&quot;* #,##0_);_(&quot;$&quot;* \(#,##0\);_(&quot;$&quot;* &quot;-&quot;??_);_(@_)"/>
   </numFmts>
   <fonts count="8" x14ac:knownFonts="1">
     <font>
@@ -337,10 +337,10 @@
     <xf numFmtId="0" fontId="3" fillId="4" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="4" borderId="2" xfId="0" applyFill="1" applyBorder="1"/>
     <xf numFmtId="164" fontId="4" fillId="4" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="168" fontId="3" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
-    <xf numFmtId="168" fontId="4" fillId="4" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="165" fontId="3" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="165" fontId="4" fillId="4" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="41" fontId="3" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
-    <xf numFmtId="168" fontId="7" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="165" fontId="7" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -652,7 +652,7 @@
     <col min="4" max="4" width="14" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="2:4" ht="19" x14ac:dyDescent="0.25">
+    <row r="1" spans="2:4" ht="19" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B1" s="1" t="s">
         <v>0</v>
       </c>
@@ -664,7 +664,7 @@
     </row>
     <row r="4" spans="2:4" x14ac:dyDescent="0.2">
       <c r="B4" s="3" t="s">
-        <v>2</v>
+        <v>17</v>
       </c>
       <c r="D4" s="4">
         <v>120</v>
@@ -672,7 +672,7 @@
     </row>
     <row r="5" spans="2:4" x14ac:dyDescent="0.2">
       <c r="B5" s="3" t="s">
-        <v>3</v>
+        <v>18</v>
       </c>
       <c r="D5" s="4">
         <v>150</v>
@@ -680,7 +680,7 @@
     </row>
     <row r="6" spans="2:4" x14ac:dyDescent="0.2">
       <c r="B6" s="3" t="s">
-        <v>4</v>
+        <v>19</v>
       </c>
       <c r="D6" s="4">
         <v>270</v>
@@ -688,7 +688,7 @@
     </row>
     <row r="7" spans="2:4" x14ac:dyDescent="0.2">
       <c r="B7" s="3" t="s">
-        <v>5</v>
+        <v>20</v>
       </c>
       <c r="D7" s="4">
         <v>300</v>
@@ -696,7 +696,7 @@
     </row>
     <row r="8" spans="2:4" x14ac:dyDescent="0.2">
       <c r="B8" s="3" t="s">
-        <v>6</v>
+        <v>21</v>
       </c>
       <c r="D8" s="4">
         <v>150</v>
@@ -704,7 +704,7 @@
     </row>
     <row r="9" spans="2:4" x14ac:dyDescent="0.2">
       <c r="B9" s="3" t="s">
-        <v>7</v>
+        <v>22</v>
       </c>
       <c r="D9" s="4">
         <v>360</v>
@@ -712,7 +712,7 @@
     </row>
     <row r="10" spans="2:4" x14ac:dyDescent="0.2">
       <c r="B10" s="3" t="s">
-        <v>8</v>
+        <v>23</v>
       </c>
       <c r="D10" s="4">
         <v>225</v>
@@ -720,7 +720,7 @@
     </row>
     <row r="11" spans="2:4" x14ac:dyDescent="0.2">
       <c r="B11" s="3" t="s">
-        <v>9</v>
+        <v>24</v>
       </c>
       <c r="D11" s="4">
         <v>210</v>
@@ -728,7 +728,7 @@
     </row>
     <row r="12" spans="2:4" x14ac:dyDescent="0.2">
       <c r="B12" s="3" t="s">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="D12" s="4">
         <v>240</v>
@@ -736,7 +736,7 @@
     </row>
     <row r="13" spans="2:4" x14ac:dyDescent="0.2">
       <c r="B13" s="3" t="s">
-        <v>11</v>
+        <v>26</v>
       </c>
       <c r="D13" s="4">
         <v>240</v>
@@ -744,7 +744,7 @@
     </row>
     <row r="14" spans="2:4" x14ac:dyDescent="0.2">
       <c r="B14" s="3" t="s">
-        <v>12</v>
+        <v>27</v>
       </c>
       <c r="D14" s="4">
         <v>450</v>
@@ -752,7 +752,7 @@
     </row>
     <row r="15" spans="2:4" x14ac:dyDescent="0.2">
       <c r="B15" s="3" t="s">
-        <v>13</v>
+        <v>28</v>
       </c>
       <c r="D15" s="4">
         <v>360</v>
@@ -760,7 +760,7 @@
     </row>
     <row r="16" spans="2:4" x14ac:dyDescent="0.2">
       <c r="B16" s="3" t="s">
-        <v>14</v>
+        <v>29</v>
       </c>
       <c r="D16" s="4">
         <v>270</v>
@@ -768,7 +768,7 @@
     </row>
     <row r="17" spans="2:4" x14ac:dyDescent="0.2">
       <c r="B17" s="3" t="s">
-        <v>15</v>
+        <v>30</v>
       </c>
       <c r="D17" s="4">
         <v>240</v>
@@ -776,7 +776,7 @@
     </row>
     <row r="18" spans="2:4" x14ac:dyDescent="0.2">
       <c r="B18" s="3" t="s">
-        <v>16</v>
+        <v>31</v>
       </c>
       <c r="D18" s="4">
         <v>300</v>
@@ -784,7 +784,7 @@
     </row>
     <row r="19" spans="2:4" x14ac:dyDescent="0.2">
       <c r="B19" s="3" t="s">
-        <v>17</v>
+        <v>32</v>
       </c>
       <c r="D19" s="4">
         <v>240</v>
@@ -792,7 +792,7 @@
     </row>
     <row r="20" spans="2:4" x14ac:dyDescent="0.2">
       <c r="B20" s="3" t="s">
-        <v>18</v>
+        <v>33</v>
       </c>
       <c r="D20" s="4">
         <v>485</v>
@@ -800,7 +800,7 @@
     </row>
     <row r="21" spans="2:4" x14ac:dyDescent="0.2">
       <c r="B21" s="3" t="s">
-        <v>19</v>
+        <v>34</v>
       </c>
       <c r="D21" s="4">
         <v>390</v>
@@ -808,7 +808,7 @@
     </row>
     <row r="22" spans="2:4" x14ac:dyDescent="0.2">
       <c r="B22" s="3" t="s">
-        <v>20</v>
+        <v>35</v>
       </c>
       <c r="D22" s="4">
         <v>500</v>
@@ -816,7 +816,7 @@
     </row>
     <row r="23" spans="2:4" x14ac:dyDescent="0.2">
       <c r="B23" s="3" t="s">
-        <v>21</v>
+        <v>36</v>
       </c>
       <c r="D23" s="4">
         <v>-500</v>
@@ -824,7 +824,7 @@
     </row>
     <row r="24" spans="2:4" x14ac:dyDescent="0.2">
       <c r="B24" s="3" t="s">
-        <v>22</v>
+        <v>37</v>
       </c>
       <c r="D24" s="4">
         <v>-400</v>
@@ -832,7 +832,7 @@
     </row>
     <row r="25" spans="2:4" x14ac:dyDescent="0.2">
       <c r="B25" s="3" t="s">
-        <v>23</v>
+        <v>38</v>
       </c>
       <c r="D25" s="4">
         <v>-300</v>
@@ -840,7 +840,7 @@
     </row>
     <row r="26" spans="2:4" x14ac:dyDescent="0.2">
       <c r="B26" s="3" t="s">
-        <v>24</v>
+        <v>39</v>
       </c>
       <c r="D26" s="4">
         <v>-650</v>
@@ -848,7 +848,7 @@
     </row>
     <row r="27" spans="2:4" x14ac:dyDescent="0.2">
       <c r="B27" s="3" t="s">
-        <v>25</v>
+        <v>40</v>
       </c>
       <c r="D27" s="4">
         <v>-650</v>
@@ -856,7 +856,7 @@
     </row>
     <row r="28" spans="2:4" x14ac:dyDescent="0.2">
       <c r="B28" s="3" t="s">
-        <v>26</v>
+        <v>41</v>
       </c>
       <c r="D28" s="4">
         <v>-650</v>
@@ -864,7 +864,7 @@
     </row>
     <row r="29" spans="2:4" x14ac:dyDescent="0.2">
       <c r="B29" s="3" t="s">
-        <v>27</v>
+        <v>42</v>
       </c>
       <c r="D29" s="4">
         <v>-400</v>
@@ -872,7 +872,7 @@
     </row>
     <row r="30" spans="2:4" x14ac:dyDescent="0.2">
       <c r="B30" s="3" t="s">
-        <v>28</v>
+        <v>43</v>
       </c>
       <c r="D30" s="4">
         <v>-2030</v>
@@ -880,7 +880,7 @@
     </row>
     <row r="31" spans="2:4" x14ac:dyDescent="0.2">
       <c r="B31" s="3" t="s">
-        <v>29</v>
+        <v>44</v>
       </c>
       <c r="D31" s="4">
         <v>-600</v>
@@ -904,7 +904,7 @@
     <col min="6" max="6" width="60" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="2:6" ht="19" x14ac:dyDescent="0.25">
+    <row r="1" spans="2:6" ht="19" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B1" s="1" t="s">
         <v>0</v>
       </c>
@@ -916,52 +916,52 @@
     </row>
     <row r="3" spans="2:6" x14ac:dyDescent="0.2">
       <c r="B3" s="5" t="s">
-        <v>30</v>
+        <v>45</v>
       </c>
       <c r="C3" s="6" t="s">
-        <v>31</v>
+        <v>46</v>
       </c>
       <c r="D3" s="5" t="s">
-        <v>32</v>
+        <v>47</v>
       </c>
       <c r="F3" s="7" t="s">
-        <v>33</v>
+        <v>48</v>
       </c>
     </row>
     <row r="4" spans="2:6" x14ac:dyDescent="0.2">
       <c r="B4" s="3" t="s">
-        <v>2</v>
+        <v>17</v>
       </c>
       <c r="C4" s="8" t="s">
-        <v>34</v>
+        <v>49</v>
       </c>
       <c r="D4" s="4">
         <v>120</v>
       </c>
       <c r="F4" s="7" t="s">
-        <v>35</v>
+        <v>50</v>
       </c>
     </row>
     <row r="5" spans="2:6" x14ac:dyDescent="0.2">
       <c r="B5" s="3" t="s">
-        <v>3</v>
+        <v>18</v>
       </c>
       <c r="C5" s="8" t="s">
-        <v>34</v>
+        <v>49</v>
       </c>
       <c r="D5" s="4">
         <v>150</v>
       </c>
       <c r="F5" s="7" t="s">
-        <v>36</v>
+        <v>51</v>
       </c>
     </row>
     <row r="6" spans="2:6" x14ac:dyDescent="0.2">
       <c r="B6" s="3" t="s">
-        <v>4</v>
+        <v>19</v>
       </c>
       <c r="C6" s="8" t="s">
-        <v>34</v>
+        <v>49</v>
       </c>
       <c r="D6" s="4">
         <v>270</v>
@@ -969,10 +969,10 @@
     </row>
     <row r="7" spans="2:6" x14ac:dyDescent="0.2">
       <c r="B7" s="3" t="s">
-        <v>5</v>
+        <v>20</v>
       </c>
       <c r="C7" s="8" t="s">
-        <v>34</v>
+        <v>49</v>
       </c>
       <c r="D7" s="4">
         <v>300</v>
@@ -980,10 +980,10 @@
     </row>
     <row r="8" spans="2:6" x14ac:dyDescent="0.2">
       <c r="B8" s="3" t="s">
-        <v>6</v>
+        <v>21</v>
       </c>
       <c r="C8" s="8" t="s">
-        <v>34</v>
+        <v>49</v>
       </c>
       <c r="D8" s="4">
         <v>150</v>
@@ -991,10 +991,10 @@
     </row>
     <row r="9" spans="2:6" x14ac:dyDescent="0.2">
       <c r="B9" s="3" t="s">
-        <v>7</v>
+        <v>22</v>
       </c>
       <c r="C9" s="8" t="s">
-        <v>34</v>
+        <v>49</v>
       </c>
       <c r="D9" s="4">
         <v>360</v>
@@ -1002,10 +1002,10 @@
     </row>
     <row r="10" spans="2:6" x14ac:dyDescent="0.2">
       <c r="B10" s="3" t="s">
-        <v>8</v>
+        <v>23</v>
       </c>
       <c r="C10" s="8" t="s">
-        <v>34</v>
+        <v>49</v>
       </c>
       <c r="D10" s="4">
         <v>225</v>
@@ -1013,10 +1013,10 @@
     </row>
     <row r="11" spans="2:6" x14ac:dyDescent="0.2">
       <c r="B11" s="3" t="s">
-        <v>9</v>
+        <v>24</v>
       </c>
       <c r="C11" s="8" t="s">
-        <v>34</v>
+        <v>49</v>
       </c>
       <c r="D11" s="4">
         <v>210</v>
@@ -1024,10 +1024,10 @@
     </row>
     <row r="12" spans="2:6" x14ac:dyDescent="0.2">
       <c r="B12" s="3" t="s">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="C12" s="8" t="s">
-        <v>34</v>
+        <v>49</v>
       </c>
       <c r="D12" s="4">
         <v>240</v>
@@ -1035,10 +1035,10 @@
     </row>
     <row r="13" spans="2:6" x14ac:dyDescent="0.2">
       <c r="B13" s="3" t="s">
-        <v>11</v>
+        <v>26</v>
       </c>
       <c r="C13" s="8" t="s">
-        <v>34</v>
+        <v>49</v>
       </c>
       <c r="D13" s="4">
         <v>240</v>
@@ -1046,10 +1046,10 @@
     </row>
     <row r="14" spans="2:6" x14ac:dyDescent="0.2">
       <c r="B14" s="3" t="s">
-        <v>12</v>
+        <v>27</v>
       </c>
       <c r="C14" s="8" t="s">
-        <v>34</v>
+        <v>49</v>
       </c>
       <c r="D14" s="4">
         <v>450</v>
@@ -1057,10 +1057,10 @@
     </row>
     <row r="15" spans="2:6" x14ac:dyDescent="0.2">
       <c r="B15" s="3" t="s">
-        <v>13</v>
+        <v>28</v>
       </c>
       <c r="C15" s="8" t="s">
-        <v>34</v>
+        <v>49</v>
       </c>
       <c r="D15" s="4">
         <v>360</v>
@@ -1068,10 +1068,10 @@
     </row>
     <row r="16" spans="2:6" x14ac:dyDescent="0.2">
       <c r="B16" s="3" t="s">
-        <v>14</v>
+        <v>29</v>
       </c>
       <c r="C16" s="8" t="s">
-        <v>34</v>
+        <v>49</v>
       </c>
       <c r="D16" s="4">
         <v>270</v>
@@ -1079,10 +1079,10 @@
     </row>
     <row r="17" spans="2:4" x14ac:dyDescent="0.2">
       <c r="B17" s="3" t="s">
-        <v>15</v>
+        <v>30</v>
       </c>
       <c r="C17" s="8" t="s">
-        <v>34</v>
+        <v>49</v>
       </c>
       <c r="D17" s="4">
         <v>240</v>
@@ -1090,10 +1090,10 @@
     </row>
     <row r="18" spans="2:4" x14ac:dyDescent="0.2">
       <c r="B18" s="3" t="s">
-        <v>16</v>
+        <v>31</v>
       </c>
       <c r="C18" s="8" t="s">
-        <v>34</v>
+        <v>49</v>
       </c>
       <c r="D18" s="4">
         <v>300</v>
@@ -1101,10 +1101,10 @@
     </row>
     <row r="19" spans="2:4" x14ac:dyDescent="0.2">
       <c r="B19" s="3" t="s">
-        <v>17</v>
+        <v>32</v>
       </c>
       <c r="C19" s="8" t="s">
-        <v>34</v>
+        <v>49</v>
       </c>
       <c r="D19" s="4">
         <v>240</v>
@@ -1112,10 +1112,10 @@
     </row>
     <row r="20" spans="2:4" x14ac:dyDescent="0.2">
       <c r="B20" s="3" t="s">
-        <v>18</v>
+        <v>33</v>
       </c>
       <c r="C20" s="8" t="s">
-        <v>34</v>
+        <v>49</v>
       </c>
       <c r="D20" s="4">
         <v>485</v>
@@ -1123,10 +1123,10 @@
     </row>
     <row r="21" spans="2:4" x14ac:dyDescent="0.2">
       <c r="B21" s="3" t="s">
-        <v>19</v>
+        <v>34</v>
       </c>
       <c r="C21" s="8" t="s">
-        <v>34</v>
+        <v>49</v>
       </c>
       <c r="D21" s="4">
         <v>390</v>
@@ -1134,10 +1134,10 @@
     </row>
     <row r="22" spans="2:4" x14ac:dyDescent="0.2">
       <c r="B22" s="3" t="s">
-        <v>20</v>
+        <v>35</v>
       </c>
       <c r="C22" s="8" t="s">
-        <v>34</v>
+        <v>49</v>
       </c>
       <c r="D22" s="4">
         <v>500</v>
@@ -1145,10 +1145,10 @@
     </row>
     <row r="23" spans="2:4" x14ac:dyDescent="0.2">
       <c r="B23" s="3" t="s">
-        <v>21</v>
+        <v>36</v>
       </c>
       <c r="C23" s="8" t="s">
-        <v>34</v>
+        <v>49</v>
       </c>
       <c r="D23" s="4">
         <v>-500</v>
@@ -1156,10 +1156,10 @@
     </row>
     <row r="24" spans="2:4" x14ac:dyDescent="0.2">
       <c r="B24" s="3" t="s">
-        <v>22</v>
+        <v>37</v>
       </c>
       <c r="C24" s="8" t="s">
-        <v>34</v>
+        <v>49</v>
       </c>
       <c r="D24" s="4">
         <v>-400</v>
@@ -1167,10 +1167,10 @@
     </row>
     <row r="25" spans="2:4" x14ac:dyDescent="0.2">
       <c r="B25" s="3" t="s">
-        <v>23</v>
+        <v>38</v>
       </c>
       <c r="C25" s="8" t="s">
-        <v>34</v>
+        <v>49</v>
       </c>
       <c r="D25" s="4">
         <v>-300</v>
@@ -1178,10 +1178,10 @@
     </row>
     <row r="26" spans="2:4" x14ac:dyDescent="0.2">
       <c r="B26" s="3" t="s">
-        <v>24</v>
+        <v>39</v>
       </c>
       <c r="C26" s="8" t="s">
-        <v>34</v>
+        <v>49</v>
       </c>
       <c r="D26" s="4">
         <v>-650</v>
@@ -1189,10 +1189,10 @@
     </row>
     <row r="27" spans="2:4" x14ac:dyDescent="0.2">
       <c r="B27" s="3" t="s">
-        <v>25</v>
+        <v>40</v>
       </c>
       <c r="C27" s="8" t="s">
-        <v>34</v>
+        <v>49</v>
       </c>
       <c r="D27" s="4">
         <v>-650</v>
@@ -1200,10 +1200,10 @@
     </row>
     <row r="28" spans="2:4" x14ac:dyDescent="0.2">
       <c r="B28" s="3" t="s">
-        <v>26</v>
+        <v>41</v>
       </c>
       <c r="C28" s="8" t="s">
-        <v>34</v>
+        <v>49</v>
       </c>
       <c r="D28" s="4">
         <v>-650</v>
@@ -1211,10 +1211,10 @@
     </row>
     <row r="29" spans="2:4" x14ac:dyDescent="0.2">
       <c r="B29" s="3" t="s">
-        <v>27</v>
+        <v>42</v>
       </c>
       <c r="C29" s="8" t="s">
-        <v>37</v>
+        <v>52</v>
       </c>
       <c r="D29" s="4">
         <v>-400</v>
@@ -1222,10 +1222,10 @@
     </row>
     <row r="30" spans="2:4" x14ac:dyDescent="0.2">
       <c r="B30" s="3" t="s">
-        <v>28</v>
+        <v>43</v>
       </c>
       <c r="C30" s="8" t="s">
-        <v>38</v>
+        <v>53</v>
       </c>
       <c r="D30" s="4">
         <v>-2030</v>
@@ -1233,10 +1233,10 @@
     </row>
     <row r="31" spans="2:4" x14ac:dyDescent="0.2">
       <c r="B31" s="3" t="s">
-        <v>29</v>
+        <v>44</v>
       </c>
       <c r="C31" s="8" t="s">
-        <v>38</v>
+        <v>53</v>
       </c>
       <c r="D31" s="4">
         <v>-600</v>
@@ -1250,7 +1250,7 @@
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0200-000000000000}">
   <dimension ref="B1:D41"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15" outlineLevelRow="1" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="2" customWidth="1"/>
     <col min="2" max="2" width="50" customWidth="1"/>
@@ -1258,7 +1258,7 @@
     <col min="4" max="4" width="14" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="2:4" ht="19" x14ac:dyDescent="0.25">
+    <row r="1" spans="2:4" ht="19" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B1" s="1" t="s">
         <v>0</v>
       </c>
@@ -1270,206 +1270,206 @@
     </row>
     <row r="4" spans="2:4" x14ac:dyDescent="0.2">
       <c r="B4" s="9" t="s">
-        <v>39</v>
+        <v>2</v>
       </c>
       <c r="C4" s="9"/>
       <c r="D4" s="9"/>
     </row>
-    <row r="5" spans="2:4" x14ac:dyDescent="0.2">
+    <row r="5" spans="2:4" outlineLevel="1" x14ac:dyDescent="0.2">
       <c r="B5" s="3" t="s">
-        <v>2</v>
+        <v>17</v>
       </c>
       <c r="D5" s="4">
         <v>120</v>
       </c>
     </row>
-    <row r="6" spans="2:4" x14ac:dyDescent="0.2">
+    <row r="6" spans="2:4" outlineLevel="1" x14ac:dyDescent="0.2">
       <c r="B6" s="3" t="s">
-        <v>3</v>
+        <v>18</v>
       </c>
       <c r="D6" s="4">
         <v>150</v>
       </c>
     </row>
-    <row r="7" spans="2:4" x14ac:dyDescent="0.2">
+    <row r="7" spans="2:4" outlineLevel="1" x14ac:dyDescent="0.2">
       <c r="B7" s="3" t="s">
-        <v>4</v>
+        <v>19</v>
       </c>
       <c r="D7" s="4">
         <v>270</v>
       </c>
     </row>
-    <row r="8" spans="2:4" x14ac:dyDescent="0.2">
+    <row r="8" spans="2:4" outlineLevel="1" x14ac:dyDescent="0.2">
       <c r="B8" s="3" t="s">
-        <v>5</v>
+        <v>20</v>
       </c>
       <c r="D8" s="4">
         <v>300</v>
       </c>
     </row>
-    <row r="9" spans="2:4" x14ac:dyDescent="0.2">
+    <row r="9" spans="2:4" outlineLevel="1" x14ac:dyDescent="0.2">
       <c r="B9" s="3" t="s">
-        <v>6</v>
+        <v>21</v>
       </c>
       <c r="D9" s="4">
         <v>150</v>
       </c>
     </row>
-    <row r="10" spans="2:4" x14ac:dyDescent="0.2">
+    <row r="10" spans="2:4" outlineLevel="1" x14ac:dyDescent="0.2">
       <c r="B10" s="3" t="s">
-        <v>7</v>
+        <v>22</v>
       </c>
       <c r="D10" s="4">
         <v>360</v>
       </c>
     </row>
-    <row r="11" spans="2:4" x14ac:dyDescent="0.2">
+    <row r="11" spans="2:4" outlineLevel="1" x14ac:dyDescent="0.2">
       <c r="B11" s="3" t="s">
-        <v>8</v>
+        <v>23</v>
       </c>
       <c r="D11" s="4">
         <v>225</v>
       </c>
     </row>
-    <row r="12" spans="2:4" x14ac:dyDescent="0.2">
+    <row r="12" spans="2:4" outlineLevel="1" x14ac:dyDescent="0.2">
       <c r="B12" s="3" t="s">
-        <v>9</v>
+        <v>24</v>
       </c>
       <c r="D12" s="4">
         <v>210</v>
       </c>
     </row>
-    <row r="13" spans="2:4" x14ac:dyDescent="0.2">
+    <row r="13" spans="2:4" outlineLevel="1" x14ac:dyDescent="0.2">
       <c r="B13" s="3" t="s">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="D13" s="4">
         <v>240</v>
       </c>
     </row>
-    <row r="14" spans="2:4" x14ac:dyDescent="0.2">
+    <row r="14" spans="2:4" outlineLevel="1" x14ac:dyDescent="0.2">
       <c r="B14" s="3" t="s">
-        <v>11</v>
+        <v>26</v>
       </c>
       <c r="D14" s="4">
         <v>240</v>
       </c>
     </row>
-    <row r="15" spans="2:4" x14ac:dyDescent="0.2">
+    <row r="15" spans="2:4" outlineLevel="1" x14ac:dyDescent="0.2">
       <c r="B15" s="3" t="s">
-        <v>12</v>
+        <v>27</v>
       </c>
       <c r="D15" s="4">
         <v>450</v>
       </c>
     </row>
-    <row r="16" spans="2:4" x14ac:dyDescent="0.2">
+    <row r="16" spans="2:4" outlineLevel="1" x14ac:dyDescent="0.2">
       <c r="B16" s="3" t="s">
-        <v>13</v>
+        <v>28</v>
       </c>
       <c r="D16" s="4">
         <v>360</v>
       </c>
     </row>
-    <row r="17" spans="2:4" x14ac:dyDescent="0.2">
+    <row r="17" spans="2:4" outlineLevel="1" x14ac:dyDescent="0.2">
       <c r="B17" s="3" t="s">
-        <v>14</v>
+        <v>29</v>
       </c>
       <c r="D17" s="4">
         <v>270</v>
       </c>
     </row>
-    <row r="18" spans="2:4" x14ac:dyDescent="0.2">
+    <row r="18" spans="2:4" outlineLevel="1" x14ac:dyDescent="0.2">
       <c r="B18" s="3" t="s">
-        <v>15</v>
+        <v>30</v>
       </c>
       <c r="D18" s="4">
         <v>240</v>
       </c>
     </row>
-    <row r="19" spans="2:4" x14ac:dyDescent="0.2">
+    <row r="19" spans="2:4" outlineLevel="1" x14ac:dyDescent="0.2">
       <c r="B19" s="3" t="s">
-        <v>16</v>
+        <v>31</v>
       </c>
       <c r="D19" s="4">
         <v>300</v>
       </c>
     </row>
-    <row r="20" spans="2:4" x14ac:dyDescent="0.2">
+    <row r="20" spans="2:4" outlineLevel="1" x14ac:dyDescent="0.2">
       <c r="B20" s="3" t="s">
-        <v>17</v>
+        <v>32</v>
       </c>
       <c r="D20" s="4">
         <v>240</v>
       </c>
     </row>
-    <row r="21" spans="2:4" x14ac:dyDescent="0.2">
+    <row r="21" spans="2:4" outlineLevel="1" x14ac:dyDescent="0.2">
       <c r="B21" s="3" t="s">
-        <v>18</v>
+        <v>33</v>
       </c>
       <c r="D21" s="4">
         <v>485</v>
       </c>
     </row>
-    <row r="22" spans="2:4" x14ac:dyDescent="0.2">
+    <row r="22" spans="2:4" outlineLevel="1" x14ac:dyDescent="0.2">
       <c r="B22" s="3" t="s">
-        <v>19</v>
+        <v>34</v>
       </c>
       <c r="D22" s="4">
         <v>390</v>
       </c>
     </row>
-    <row r="23" spans="2:4" x14ac:dyDescent="0.2">
+    <row r="23" spans="2:4" outlineLevel="1" x14ac:dyDescent="0.2">
       <c r="B23" s="3" t="s">
-        <v>20</v>
+        <v>35</v>
       </c>
       <c r="D23" s="4">
         <v>500</v>
       </c>
     </row>
-    <row r="24" spans="2:4" x14ac:dyDescent="0.2">
+    <row r="24" spans="2:4" outlineLevel="1" x14ac:dyDescent="0.2">
       <c r="B24" s="3" t="s">
-        <v>21</v>
+        <v>36</v>
       </c>
       <c r="D24" s="4">
         <v>-500</v>
       </c>
     </row>
-    <row r="25" spans="2:4" x14ac:dyDescent="0.2">
+    <row r="25" spans="2:4" outlineLevel="1" x14ac:dyDescent="0.2">
       <c r="B25" s="3" t="s">
-        <v>22</v>
+        <v>37</v>
       </c>
       <c r="D25" s="4">
         <v>-400</v>
       </c>
     </row>
-    <row r="26" spans="2:4" x14ac:dyDescent="0.2">
+    <row r="26" spans="2:4" outlineLevel="1" x14ac:dyDescent="0.2">
       <c r="B26" s="3" t="s">
-        <v>23</v>
+        <v>38</v>
       </c>
       <c r="D26" s="4">
         <v>-300</v>
       </c>
     </row>
-    <row r="27" spans="2:4" x14ac:dyDescent="0.2">
+    <row r="27" spans="2:4" outlineLevel="1" x14ac:dyDescent="0.2">
       <c r="B27" s="3" t="s">
-        <v>24</v>
+        <v>39</v>
       </c>
       <c r="D27" s="4">
         <v>-650</v>
       </c>
     </row>
-    <row r="28" spans="2:4" x14ac:dyDescent="0.2">
+    <row r="28" spans="2:4" outlineLevel="1" x14ac:dyDescent="0.2">
       <c r="B28" s="3" t="s">
-        <v>25</v>
+        <v>40</v>
       </c>
       <c r="D28" s="4">
         <v>-650</v>
       </c>
     </row>
-    <row r="29" spans="2:4" x14ac:dyDescent="0.2">
+    <row r="29" spans="2:4" outlineLevel="1" x14ac:dyDescent="0.2">
       <c r="B29" s="3" t="s">
-        <v>26</v>
+        <v>41</v>
       </c>
       <c r="D29" s="4">
         <v>-650</v>
@@ -1477,7 +1477,7 @@
     </row>
     <row r="30" spans="2:4" x14ac:dyDescent="0.2">
       <c r="B30" s="10" t="s">
-        <v>40</v>
+        <v>6</v>
       </c>
       <c r="C30" s="11"/>
       <c r="D30" s="12">
@@ -1487,14 +1487,14 @@
     </row>
     <row r="32" spans="2:4" x14ac:dyDescent="0.2">
       <c r="B32" s="9" t="s">
-        <v>41</v>
+        <v>7</v>
       </c>
       <c r="C32" s="9"/>
       <c r="D32" s="9"/>
     </row>
-    <row r="33" spans="2:4" x14ac:dyDescent="0.2">
+    <row r="33" spans="2:4" outlineLevel="1" x14ac:dyDescent="0.2">
       <c r="B33" s="3" t="s">
-        <v>27</v>
+        <v>42</v>
       </c>
       <c r="D33" s="4">
         <v>-400</v>
@@ -1502,7 +1502,7 @@
     </row>
     <row r="34" spans="2:4" x14ac:dyDescent="0.2">
       <c r="B34" s="10" t="s">
-        <v>42</v>
+        <v>9</v>
       </c>
       <c r="C34" s="11"/>
       <c r="D34" s="12">
@@ -1512,22 +1512,22 @@
     </row>
     <row r="36" spans="2:4" x14ac:dyDescent="0.2">
       <c r="B36" s="9" t="s">
-        <v>43</v>
+        <v>10</v>
       </c>
       <c r="C36" s="9"/>
       <c r="D36" s="9"/>
     </row>
-    <row r="37" spans="2:4" x14ac:dyDescent="0.2">
+    <row r="37" spans="2:4" outlineLevel="1" x14ac:dyDescent="0.2">
       <c r="B37" s="3" t="s">
-        <v>28</v>
+        <v>43</v>
       </c>
       <c r="D37" s="4">
         <v>-2030</v>
       </c>
     </row>
-    <row r="38" spans="2:4" x14ac:dyDescent="0.2">
+    <row r="38" spans="2:4" outlineLevel="1" x14ac:dyDescent="0.2">
       <c r="B38" s="3" t="s">
-        <v>29</v>
+        <v>44</v>
       </c>
       <c r="D38" s="4">
         <v>-600</v>
@@ -1535,7 +1535,7 @@
     </row>
     <row r="39" spans="2:4" x14ac:dyDescent="0.2">
       <c r="B39" s="10" t="s">
-        <v>44</v>
+        <v>13</v>
       </c>
       <c r="C39" s="11"/>
       <c r="D39" s="12">
@@ -1545,7 +1545,7 @@
     </row>
     <row r="41" spans="2:4" x14ac:dyDescent="0.2">
       <c r="B41" s="10" t="s">
-        <v>45</v>
+        <v>14</v>
       </c>
       <c r="C41" s="11"/>
       <c r="D41" s="12">
@@ -1561,7 +1561,7 @@
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0300-000000000000}">
   <dimension ref="B1:D21"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15" outlineLevelRow="1" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="2" customWidth="1"/>
     <col min="2" max="2" width="50" customWidth="1"/>
@@ -1569,7 +1569,7 @@
     <col min="4" max="4" width="14" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="2:4" ht="19" x14ac:dyDescent="0.25">
+    <row r="1" spans="2:4" ht="19" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B1" s="1" t="s">
         <v>0</v>
       </c>
@@ -1581,30 +1581,30 @@
     </row>
     <row r="4" spans="2:4" x14ac:dyDescent="0.2">
       <c r="B4" s="9" t="s">
-        <v>39</v>
+        <v>2</v>
       </c>
       <c r="C4" s="9"/>
       <c r="D4" s="9"/>
     </row>
-    <row r="5" spans="2:4" x14ac:dyDescent="0.2">
+    <row r="5" spans="2:4" outlineLevel="1" x14ac:dyDescent="0.2">
       <c r="B5" s="3" t="s">
-        <v>46</v>
+        <v>3</v>
       </c>
       <c r="D5" s="13">
         <v>5500</v>
       </c>
     </row>
-    <row r="6" spans="2:4" x14ac:dyDescent="0.2">
+    <row r="6" spans="2:4" outlineLevel="1" x14ac:dyDescent="0.2">
       <c r="B6" s="3" t="s">
-        <v>47</v>
+        <v>4</v>
       </c>
       <c r="D6" s="15">
         <v>-1200</v>
       </c>
     </row>
-    <row r="7" spans="2:4" x14ac:dyDescent="0.2">
+    <row r="7" spans="2:4" outlineLevel="1" x14ac:dyDescent="0.2">
       <c r="B7" s="3" t="s">
-        <v>48</v>
+        <v>5</v>
       </c>
       <c r="D7" s="15">
         <v>-1950</v>
@@ -1612,7 +1612,7 @@
     </row>
     <row r="8" spans="2:4" x14ac:dyDescent="0.2">
       <c r="B8" s="10" t="s">
-        <v>40</v>
+        <v>6</v>
       </c>
       <c r="C8" s="11"/>
       <c r="D8" s="14">
@@ -1622,14 +1622,14 @@
     </row>
     <row r="10" spans="2:4" x14ac:dyDescent="0.2">
       <c r="B10" s="9" t="s">
-        <v>41</v>
+        <v>7</v>
       </c>
       <c r="C10" s="9"/>
       <c r="D10" s="9"/>
     </row>
-    <row r="11" spans="2:4" x14ac:dyDescent="0.2">
+    <row r="11" spans="2:4" outlineLevel="1" x14ac:dyDescent="0.2">
       <c r="B11" s="3" t="s">
-        <v>49</v>
+        <v>8</v>
       </c>
       <c r="D11" s="13">
         <v>-400</v>
@@ -1637,7 +1637,7 @@
     </row>
     <row r="12" spans="2:4" x14ac:dyDescent="0.2">
       <c r="B12" s="10" t="s">
-        <v>42</v>
+        <v>9</v>
       </c>
       <c r="C12" s="11"/>
       <c r="D12" s="14">
@@ -1647,22 +1647,22 @@
     </row>
     <row r="14" spans="2:4" x14ac:dyDescent="0.2">
       <c r="B14" s="9" t="s">
-        <v>43</v>
+        <v>10</v>
       </c>
       <c r="C14" s="9"/>
       <c r="D14" s="9"/>
     </row>
-    <row r="15" spans="2:4" x14ac:dyDescent="0.2">
+    <row r="15" spans="2:4" outlineLevel="1" x14ac:dyDescent="0.2">
       <c r="B15" s="3" t="s">
-        <v>50</v>
+        <v>11</v>
       </c>
       <c r="D15" s="13">
         <v>-2030</v>
       </c>
     </row>
-    <row r="16" spans="2:4" x14ac:dyDescent="0.2">
+    <row r="16" spans="2:4" outlineLevel="1" x14ac:dyDescent="0.2">
       <c r="B16" s="3" t="s">
-        <v>51</v>
+        <v>12</v>
       </c>
       <c r="D16" s="15">
         <v>-600</v>
@@ -1670,7 +1670,7 @@
     </row>
     <row r="17" spans="2:4" x14ac:dyDescent="0.2">
       <c r="B17" s="10" t="s">
-        <v>44</v>
+        <v>13</v>
       </c>
       <c r="C17" s="11"/>
       <c r="D17" s="14">
@@ -1678,9 +1678,9 @@
         <v>-2630</v>
       </c>
     </row>
-    <row r="19" spans="2:4" x14ac:dyDescent="0.2">
+    <row r="19" spans="2:4" outlineLevel="1" x14ac:dyDescent="0.2">
       <c r="B19" s="10" t="s">
-        <v>45</v>
+        <v>14</v>
       </c>
       <c r="C19" s="11"/>
       <c r="D19" s="14">
@@ -1688,9 +1688,9 @@
         <v>-680</v>
       </c>
     </row>
-    <row r="20" spans="2:4" x14ac:dyDescent="0.2">
+    <row r="20" spans="2:4" outlineLevel="1" x14ac:dyDescent="0.2">
       <c r="B20" s="3" t="s">
-        <v>52</v>
+        <v>15</v>
       </c>
       <c r="D20" s="16">
         <v>1300</v>
@@ -1698,7 +1698,7 @@
     </row>
     <row r="21" spans="2:4" x14ac:dyDescent="0.2">
       <c r="B21" s="10" t="s">
-        <v>53</v>
+        <v>16</v>
       </c>
       <c r="C21" s="11"/>
       <c r="D21" s="14">
